--- a/DVLA.UI/wwwroot/Template/ResultUploadTemplate.xlsx
+++ b/DVLA.UI/wwwroot/Template/ResultUploadTemplate.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F185D2-DA55-491F-9B1A-1663ABB3EEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t>TestType</t>
   </si>
@@ -228,12 +240,21 @@
   </si>
   <si>
     <t>08053046111</t>
+  </si>
+  <si>
+    <t>NationalID</t>
+  </si>
+  <si>
+    <t>PassportNumber</t>
+  </si>
+  <si>
+    <t>DvlaLicenseNumber</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -313,9 +334,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -353,9 +374,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -390,7 +411,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -425,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -598,8 +619,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -633,9 +654,11 @@
     <col min="31" max="31" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -735,8 +758,17 @@
       <c r="AG1" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -827,6 +859,15 @@
       </c>
       <c r="AG2" t="s">
         <v>57</v>
+      </c>
+      <c r="AH2">
+        <v>43728</v>
+      </c>
+      <c r="AI2">
+        <v>5393</v>
+      </c>
+      <c r="AJ2">
+        <v>49639</v>
       </c>
     </row>
   </sheetData>
@@ -835,49 +876,49 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$3</xm:f>
           </x14:formula1>
           <xm:sqref>A1:A1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>C1:C1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>F1:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>Sheet2!$D$2:$D$10</xm:f>
           </x14:formula1>
           <xm:sqref>O1:T1048576 X1:X1048576 Z1:AB1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$10</xm:f>
           </x14:formula1>
           <xm:sqref>U1:V1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
             <xm:f>Sheet2!$F$2:$F$25</xm:f>
           </x14:formula1>
           <xm:sqref>AC1:AC1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>Sheet2!$G$2:$G$3</xm:f>
           </x14:formula1>
           <xm:sqref>AF1:AF1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>Sheet2!$H$2:$H$4</xm:f>
           </x14:formula1>
@@ -890,7 +931,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
